--- a/docs/zoho-books-webhook-websocket-api-conservation-plan.xlsx
+++ b/docs/zoho-books-webhook-websocket-api-conservation-plan.xlsx
@@ -504,9 +504,6 @@
           <t>Zoho Books — Webhook / WebSocket API Conservation Plan (REVISED)</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr"/>
-      <c r="C1" t="inlineStr"/>
-      <c r="D1" t="inlineStr"/>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -514,9 +511,6 @@
           <t>Generated: 2026-08-31 | Revised after codebase verification</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -524,15 +518,6 @@
           <t>Source: docs/zoho-books-apis-webhooks-module-wise.xlsx</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr"/>
-      <c r="B4" t="inlineStr"/>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
@@ -673,8 +658,6 @@
           <t>listDeliveryChallans + applyDeliveryChallans exist in ZohoSyncService.pullOrderTracking as best-effort legacy</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -687,8 +670,6 @@
           <t>Remove delivery challan API call from tracking pull; do NOT build webhook for delivery challans</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr"/>
@@ -702,9 +683,6 @@
           <t>Current API waste (highest impact)</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr"/>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -749,22 +727,24 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="n">
-        <v>2</v>
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Order tracking — packages/shipments</t>
+          <t>Order tracking - packages/shipments</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Scheduler every 15 min: GET salesorder + GET packages (Inventory API)</t>
+          <t>Shipment webhook live on UAT; scheduler fallback can still GET salesorder + packages</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Zoho Inventory workflow webhook on Package/Shipment events</t>
+          <t>Zoho Inventory workflow webhook deployed for package/shipment events</t>
         </is>
       </c>
     </row>
@@ -820,9 +800,6 @@
           <t>Recommendation priority (revised)</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr"/>
-      <c r="C23" t="inlineStr"/>
-      <c r="D23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -835,8 +812,6 @@
           <t>Expand stock webhook coverage</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr"/>
-      <c r="D24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -846,11 +821,9 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Package/Shipment webhooks (Zoho Inventory) → replace tracking poll</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr"/>
-      <c r="D25" t="inlineStr"/>
+          <t>Package/Shipment webhooks deployed on UAT; use scheduler as fallback only</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -863,8 +836,6 @@
           <t>Remove delivery challan call from pullOrderTracking (dead code cleanup)</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr"/>
-      <c r="D26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -877,8 +848,6 @@
           <t>Item created/edited webhooks → replace product pull pagination</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr"/>
-      <c r="D27" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1322,7 +1291,7 @@
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>Zoho Inventory workflow webhook: Package Created, Shipment Delivered</t>
+          <t>Zoho Inventory workflow webhook: Package Created, Shipment Updated, Shipment Delivered</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -1332,17 +1301,17 @@
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>POST /api/v1/zoho/shipment-webhook (NEW)</t>
+          <t>POST /api/v1/zoho/shipment-webhook</t>
         </is>
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
-          <t>ZohoShipmentWebhookHandler (NEW)</t>
+          <t>ZohoShipmentWebhookHandlerService</t>
         </is>
       </c>
       <c r="M3" s="3" t="inlineStr">
         <is>
-          <t>TO BUILD</t>
+          <t>LIVE ON UAT</t>
         </is>
       </c>
       <c r="N3" s="3" t="inlineStr">
@@ -1352,7 +1321,7 @@
       </c>
       <c r="O3" s="3" t="inlineStr">
         <is>
-          <t>PRIMARY path. Package created → HAND_WRAPPED. Shipment status=delivered OR fulfilled+shipment_id → FULFILLED. Mirrors applyPackages() logic.</t>
+          <t>Primary path is now event-driven. UAT route returns 401 without auth, backend jar contains handler, and zoho_shipment_webhook_event table is applied. Scheduler/admin pull remains fallback.</t>
         </is>
       </c>
     </row>
@@ -1399,7 +1368,7 @@
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>Webhook on Sales Order Edited (tracking fields only) OR embed in shipment webhook</t>
+          <t>Embed tracking fields in shipment webhook payload; keep SO GET as fallback</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
@@ -1414,12 +1383,12 @@
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>ZohoShipmentWebhookHandler</t>
+          <t>ZohoShipmentWebhookHandlerService</t>
         </is>
       </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
-          <t>TO BUILD</t>
+          <t>PARTIAL - WEBHOOK LIVE</t>
         </is>
       </c>
       <c r="N4" s="3" t="inlineStr">
@@ -1429,7 +1398,7 @@
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t>Can reduce SO GET if webhook payload includes tracking_number, delivery_method, shipment_date, line_items quantities.</t>
+          <t>Webhook can carry AWB/carrier/shipment date. Sales-order GET may still run only in scheduler/admin fallback or when payload lacks fields.</t>
         </is>
       </c>
     </row>
@@ -1977,7 +1946,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Phase 1a</t>
+          <t>Phase 1a - Done</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -1992,17 +1961,17 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>New ZohoShipmentWebhookHandler — reuse applyPackages() logic</t>
+          <t>ZohoShipmentWebhookHandlerService + ZohoOrderStatus.applyPackages</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>GET /inventory/v1/packages on every tracking poll</t>
+          <t>Previous recurring GET /inventory/v1/packages tracking poll; now scheduler/admin fallback only</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>PRIMARY delivery path. Ops marks shipment Delivered → admin FULFILLED.</t>
+          <t>Live on UAT; DB table zoho_shipment_webhook_event applied. Scheduler remains fallback.</t>
         </is>
       </c>
     </row>
@@ -2056,12 +2025,12 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>Feature flag; increase order-tracking.fixed-delay-ms to 24h when webhooks active</t>
+          <t>Feature flag; increase order-tracking.fixed-delay-ms once workflow logs are stable</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>15-min scheduler poll</t>
+          <t>15-min scheduler fallback</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
@@ -2260,7 +2229,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>N/A — Ledgerly may use different signal</t>
+          <t>N/A - Ledgerly may use different signal</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
@@ -2275,12 +2244,12 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>DONE via pull — applyPackages</t>
+          <t>DONE via shipment webhook + fallback pull</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>Webhook: package.created → HAND_WRAPPED</t>
+          <t>LIVE: shipment-webhook -&gt; HAND_WRAPPED</t>
         </is>
       </c>
     </row>
@@ -2302,17 +2271,17 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>Package→Shipment with AWB</t>
+          <t>Package-&gt;Shipment with AWB</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>DONE via pull — applyPackages</t>
+          <t>DONE via shipment webhook + fallback pull</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>Webhook: shipment.updated → tracking fields</t>
+          <t>LIVE: shipment-webhook updates tracking fields</t>
         </is>
       </c>
     </row>
@@ -2339,12 +2308,12 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>DONE via pull — isFulfilledShipment</t>
+          <t>DONE via shipment webhook + fallback pull</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>Webhook: shipment.delivered → FULFILLED</t>
+          <t>LIVE: shipment-webhook -&gt; FULFILLED</t>
         </is>
       </c>
     </row>
@@ -2545,7 +2514,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>POST /api/v1/zoho/shipment-webhook (NEW)</t>
+          <t>POST /api/v1/zoho/shipment-webhook</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -2555,7 +2524,7 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>X-Zoho-Shipment-Signature</t>
+          <t>X-Zoho-Shipment-Signature or X-Zoho-Shipment-Secret</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
@@ -2575,7 +2544,7 @@
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>TO BUILD — P1</t>
+          <t>LIVE ON UAT</t>
         </is>
       </c>
     </row>
@@ -2716,7 +2685,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
@@ -2776,12 +2744,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Yes — our backend could push tracking updates to browser via SSE/WebSocket after receiving Zoho webhook.</t>
+          <t>Yes - our backend could push tracking updates to browser via SSE/WebSocket after receiving Zoho webhook.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Optional Phase 4: Server-Sent Events on /api/v1/orders/{id}/tracking-stream to replace 60s frontend polling (useOrderTrackingPoll). This conserves OUR server load, not Zoho API quota.</t>
+          <t>Optional Phase 4: Server-Sent Events on /api/v1/orders/{id}/tracking-stream. Frontend order-tracking API polling has already been removed.</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2761,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>useOrderTrackingPoll.ts polls every 60s while order non-terminal. Public track page does NOT trigger server Zoho refresh.</t>
+          <t>Removed. useOrderTracking fetches initial selected order tracking and exposes manual refresh; no 60s interval polling remains.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>After tracking webhooks update DB, polling interval can increase to 5 min or switch to SSE push.</t>
+          <t>Tracking webhooks update DB. Optional SSE/WebSocket would be for realtime UX only, not Zoho quota.</t>
         </is>
       </c>
     </row>
@@ -2819,7 +2787,6 @@
         </is>
       </c>
     </row>
-    <row r="9"/>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>

--- a/docs/zoho-books-webhook-websocket-api-conservation-plan.xlsx
+++ b/docs/zoho-books-webhook-websocket-api-conservation-plan.xlsx
@@ -519,6 +519,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
@@ -845,7 +846,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Item created/edited webhooks → replace product pull pagination</t>
+          <t>Item/catalog webhook deployed on UAT; full/incremental pulls are fallback/backfill only</t>
         </is>
       </c>
     </row>
@@ -1522,7 +1523,7 @@
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>Item created/edited webhook → single SKU pull</t>
+          <t>Item created/edited webhook -&gt; single item pull/merge; full/incremental pull remains fallback</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
@@ -1532,17 +1533,17 @@
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t>POST /api/v1/zoho/item-webhook (NEW)</t>
+          <t>POST /api/v1/zoho/item-webhook</t>
         </is>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
-          <t>ZohoItemWebhookHandler (NEW)</t>
+          <t>ZohoItemWebhookHandlerService</t>
         </is>
       </c>
       <c r="M6" s="3" t="inlineStr">
         <is>
-          <t>TO BUILD</t>
+          <t>LIVE ON UAT</t>
         </is>
       </c>
       <c r="N6" s="3" t="inlineStr">
@@ -1552,7 +1553,7 @@
       </c>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t>Ledgerly item.updated webhook already done.</t>
+          <t>UAT route/auth verified. Persists zoho_item_webhook_event. Handler calls ZohoSyncService.pullExternalProduct for edge cases: SKU rename, inactive item, variants, image/category merge conflicts.</t>
         </is>
       </c>
     </row>
@@ -1599,7 +1600,7 @@
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>Embed fields in item webhook body to skip GET</t>
+          <t>Item created/edited webhook -&gt; single item pull/merge; full/incremental pull remains fallback</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
@@ -1614,12 +1615,12 @@
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
-          <t>ZohoItemWebhookHandler + ZohoProductFieldMapper</t>
+          <t>ZohoItemWebhookHandlerService</t>
         </is>
       </c>
       <c r="M7" s="3" t="inlineStr">
         <is>
-          <t>TO BUILD</t>
+          <t>LIVE ON UAT</t>
         </is>
       </c>
       <c r="N7" s="3" t="inlineStr">
@@ -1627,7 +1628,11 @@
           <t>60–90%</t>
         </is>
       </c>
-      <c r="O7" s="3" t="inlineStr"/>
+      <c r="O7" s="3" t="inlineStr">
+        <is>
+          <t>UAT route/auth verified. Persists zoho_item_webhook_event. Handler calls ZohoSyncService.pullExternalProduct for edge cases: SKU rename, inactive item, variants, image/category merge conflicts.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
@@ -2042,12 +2047,12 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>Phase 2</t>
+          <t>Phase 2 - Done</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Item catalog webhook</t>
+          <t>Item/catalog webhook for item created/edited/inactive events</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
@@ -2057,12 +2062,12 @@
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>ZohoItemWebhookHandler</t>
+          <t>DONE: ZohoItemWebhookHandlerService + idempotency table + UAT route/auth verification</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>Product pull list pagination</t>
+          <t>Full/incremental item-list scans for changed rows; pull-products remains fallback/backfill</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
@@ -2074,12 +2079,12 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Phase 3</t>
+          <t>Phase 3 - Done</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Order void webhook</t>
+          <t>Sales-order status/void webhook</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
@@ -2089,12 +2094,12 @@
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>ZohoOrderStatusWebhookHandler</t>
+          <t>DONE: ZohoOrderStatusWebhookHandlerService + idempotency table + UAT route/auth verification</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>Void detection via tracking pull</t>
+          <t>Void detection through tracking fallback pulls</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
@@ -2180,12 +2185,12 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>NOT IMPLEMENTED</t>
+          <t>DONE via item webhook + fallback pull</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>Phase 2 — ZohoItemWebhookHandler</t>
+          <t>LIVE: item-webhook -&gt; single item merge</t>
         </is>
       </c>
     </row>
@@ -2424,7 +2429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -2561,12 +2566,12 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>X-Zoho-Item-Signature</t>
+          <t>X-Zoho-Item-Signature or X-Zoho-Item-Secret</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>{ eventId, sku, zohoItemId, fields? }</t>
+          <t>{ eventId?, item_id?, sku?, status?, last_modified_time? }</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
@@ -2576,12 +2581,12 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>ZohoProductFieldMapper + merge</t>
+          <t>ZohoItemWebhookHandlerService + ZohoSyncService.pullExternalProduct</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>TO BUILD — P2</t>
+          <t>LIVE ON UAT</t>
         </is>
       </c>
     </row>
@@ -2656,6 +2661,43 @@
       <c r="G6" s="9" t="inlineStr">
         <is>
           <t>DEPRECATE</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>POST /api/v1/zoho/order-status-webhook</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>X-Zoho-Order-Status-Signature or X-Zoho-Order-Status-Secret</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>{ eventId?, salesorder_id?, salesorder_number?, status, tracking fields? }</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Sales Order status/void workflow</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>ZohoOrderStatusWebhookHandlerService + ZohoOrderStatus</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>LIVE ON UAT</t>
         </is>
       </c>
     </row>
@@ -2685,6 +2727,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
@@ -2715,7 +2758,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Use inbound HTTP webhooks only.</t>
+          <t>Use inbound HTTP webhooks; item, shipment, stock, and order-status webhooks are now implemented on UAT.</t>
         </is>
       </c>
     </row>
@@ -2787,6 +2830,7 @@
         </is>
       </c>
     </row>
+    <row r="9"/>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
@@ -2858,7 +2902,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>P4 — nice to have</t>
+          <t>Optional only for realtime browser UX; all Zoho quota-saving webhook work in this workbook is now done on UAT.</t>
         </is>
       </c>
     </row>
